--- a/fapiao-templates/hechi_uk.xlsx
+++ b/fapiao-templates/hechi_uk.xlsx
@@ -2023,60 +2023,6 @@
     <mergeCell ref="F15:H15"/>
     <mergeCell ref="I7:K7"/>
   </mergeCells>
-  <dataValidations count="13">
-    <dataValidation sqref="B2:D2" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop" operator="between">
-      <formula1>#REF!</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation sqref="B3:D3" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop" operator="between">
-      <formula1>#REF!</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation sqref="B6:D6 B8:D8" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="当前地址超长度··" error="当前地址超长度，请控制在35个字符内" promptTitle="地址请控制在35个字符内，不然无法制单" prompt="地址请控制在35个字符内，不然无法制单" type="textLength" errorStyle="stop" operator="between">
-      <formula1>0</formula1>
-      <formula2>35</formula2>
-    </dataValidation>
-    <dataValidation sqref="F6:H6" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop" operator="between">
-      <formula1>"买单报关,9810,9710,0110"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation sqref="B7:D7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="当前地址超长度··" error="当前地址超长度，请控制在35个字符内" promptTitle="地址请控制在35个字符内，不然无法制单" prompt="地址请控制在35个字符内，不然无法制单" type="textLength" errorStyle="stop" operator="between">
-      <formula1>0</formula1>
-      <formula2>500</formula2>
-    </dataValidation>
-    <dataValidation sqref="F8:H8" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop" operator="between">
-      <formula1>"不包税,包税,自税递延"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation sqref="F12:H12" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop" operator="between">
-      <formula1>"卡派,快递派"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation sqref="Z17" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop" operator="between">
-      <formula1>"私人地址,商业地址,海外仓地址,亚马逊地址"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation sqref="X1:X15 X18:X1018" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="炜易达提醒您" error="你选择是或者否 即可" type="list" errorStyle="stop" operator="between">
-      <formula1>"是,否"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation sqref="AA1:AA16 AA18:AA1018" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop" operator="between">
-      <formula1>"私人地址,海外仓地址,商业地址,亚马逊地址"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation sqref="AB1:AB16 AB18:AB1018" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop" operator="between">
-      <formula1>"是,否"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation sqref="F1:H5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop" operator="between">
-      <formula1>"否,是"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation sqref="B4:D5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="当前地址超长度··" error="当前地址超长度，请控制在35个字符内" type="textLength" errorStyle="stop" operator="between">
-      <formula1>0</formula1>
-      <formula2>35</formula2>
-    </dataValidation>
-  </dataValidations>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
